--- a/artfynd/A 58682-2020 artfynd.xlsx
+++ b/artfynd/A 58682-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123184222</v>
       </c>
       <c r="B2" t="n">
-        <v>105322</v>
+        <v>105337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58682-2020 artfynd.xlsx
+++ b/artfynd/A 58682-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123184222</v>
       </c>
       <c r="B2" t="n">
-        <v>105337</v>
+        <v>105339</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58682-2020 artfynd.xlsx
+++ b/artfynd/A 58682-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123184222</v>
       </c>
       <c r="B2" t="n">
-        <v>105339</v>
+        <v>104914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
